--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:13</t>
+    <t xml:space="preserve">2026-08-17 16:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:02</t>
+    <t xml:space="preserve">2026-08-17 20:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 20:25</t>
+    <t xml:space="preserve">2026-09-06 21:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
